--- a/lab1/out/lab1_recalculated.xlsx
+++ b/lab1/out/lab1_recalculated.xlsx
@@ -34,11 +34,13 @@
     <definedName function="false" hidden="false" name="p_interval_min" vbProcedure="false">Параметри!$C$4</definedName>
     <definedName function="false" hidden="false" name="p_kwh_m2_year" vbProcedure="false">Параметри!$C$6</definedName>
     <definedName function="false" hidden="false" name="p_meters" vbProcedure="false">Параметри!$C$3</definedName>
-    <definedName function="false" hidden="false" name="p_price_hypothesis" vbProcedure="false">Параметри!$C$24</definedName>
+    <definedName function="false" hidden="false" name="p_mvp_months" vbProcedure="false">Параметри!$C$24</definedName>
+    <definedName function="false" hidden="false" name="p_price_hypothesis" vbProcedure="false">Параметри!$C$26</definedName>
     <definedName function="false" hidden="false" name="p_sim_month" vbProcedure="false">Параметри!$C$17</definedName>
     <definedName function="false" hidden="false" name="p_support_hours" vbProcedure="false">Параметри!$C$20</definedName>
     <definedName function="false" hidden="false" name="p_support_rate" vbProcedure="false">Параметри!$C$21</definedName>
     <definedName function="false" hidden="false" name="p_tariff" vbProcedure="false">Параметри!$C$7</definedName>
+    <definedName function="false" hidden="false" name="p_team_size" vbProcedure="false">Параметри!$C$25</definedName>
     <definedName function="false" hidden="false" name="p_tech_hours_as_is" vbProcedure="false">Параметри!$C$13</definedName>
     <definedName function="false" hidden="false" name="p_tech_hours_to_be" vbProcedure="false">Параметри!$C$14</definedName>
     <definedName function="false" hidden="false" name="p_tech_rate" vbProcedure="false">Параметри!$C$15</definedName>
@@ -54,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="328">
   <si>
     <t xml:space="preserve">Поле</t>
   </si>
@@ -95,13 +97,13 @@
     <t xml:space="preserve">Ціннісна пропозиція</t>
   </si>
   <si>
-    <t xml:space="preserve">Виявлення аномалії протягом 2 год замість 12 діб і встановлення її причини до рахунку; оцінена цінність 10 800 EUR на будівлю за рік (П)</t>
+    <t xml:space="preserve">Медіанний час виявлення аномалії не більше 2 год замість 12 діб і встановлення її причини до рахунку; оцінена цінність 10 800 EUR на будівлю за рік (П)</t>
   </si>
   <si>
     <t xml:space="preserve">Ключова метрика</t>
   </si>
   <si>
-    <t xml:space="preserve">Медіана часу від початку аномалії до її фіксації: база 288 год (П), ціль не більше 2 год для 80% аномалій за 3 міс.</t>
+    <t xml:space="preserve">Медіана часу від початку аномалії до її фіксації: база 288 год (П), ціль: медіана не більше 2 год за 3 міс. пілоту; додатковий контроль хвоста розподілу: P80 не більше 4 год</t>
   </si>
   <si>
     <t xml:space="preserve">Межі MVP</t>
@@ -395,6 +397,27 @@
     <t xml:space="preserve">умова варіанта ЛР № 4 і № 5</t>
   </si>
   <si>
+    <t xml:space="preserve">p_mvp_months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Строк розроблення MVP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">міс.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p_team_size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Чисельність команди MVP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">осіб</t>
+  </si>
+  <si>
+    <t xml:space="preserve">умова варіанта ЛР № 4 і № 5: BA/PM, 2 розробники, QA, DevOps</t>
+  </si>
+  <si>
     <t xml:space="preserve">p_price_hypothesis</t>
   </si>
   <si>
@@ -566,6 +589,9 @@
     <t xml:space="preserve">Пріоритет залучення</t>
   </si>
   <si>
+    <t xml:space="preserve">Квадрант</t>
+  </si>
+  <si>
     <t xml:space="preserve">Конфлікт, ризик</t>
   </si>
   <si>
@@ -743,13 +769,13 @@
     <t xml:space="preserve">Delivery</t>
   </si>
   <si>
-    <t xml:space="preserve">Розроблення backend, frontend і ПЗ шлюзу (2 розробники)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">обсяг scope, SP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тестування і тестовий стенд з 6 типами лічильників</t>
+    <t xml:space="preserve">Розроблення MVP командою з 5 осіб протягом 7 міс.: BA/PM, 2 розробники (backend, frontend, ПЗ шлюзу), QA, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">обсяг scope, SP; FTE ролей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тестовий стенд з 6 типами лічильників</t>
   </si>
   <si>
     <t xml:space="preserve">кількість типів лічильників</t>
@@ -1495,7 +1521,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -1543,7 +1569,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
@@ -2022,16 +2048,56 @@
         <v>114</v>
       </c>
       <c r="C24" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>115</v>
+      <c r="F26" s="2" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2070,12 +2136,12 @@
         <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B2" s="4" t="n">
         <f aca="false">1440/p_interval_min</f>
@@ -2085,12 +2151,12 @@
         <v>35</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B3" s="4" t="n">
         <f aca="false">p_meters*B2*p_days_month</f>
@@ -2100,27 +2166,27 @@
         <v>35</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B4" s="4" t="n">
         <f aca="false">p_area_m2*p_kwh_m2_year</f>
         <v>1920000</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B5" s="4" t="n">
         <f aca="false">B4*p_tariff</f>
@@ -2130,132 +2196,132 @@
         <v>86</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B6" s="4" t="n">
         <f aca="false">p_delta_kw*p_anomaly_hours_day*p_days_as_is*p_anomalies_month*12</f>
         <v>64800</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B7" s="4" t="n">
         <f aca="false">p_delta_kw*p_anomaly_hours_day*p_days_to_be*p_anomalies_month*12</f>
         <v>5400</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B8" s="5" t="n">
         <f aca="false">B6/B4</f>
         <v>0.03375</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B9" s="4" t="n">
         <f aca="false">B6-B7</f>
         <v>59400</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B10" s="5" t="n">
         <f aca="false">B9/B4</f>
         <v>0.0309375</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B11" s="4" t="n">
         <f aca="false">B9*p_tariff</f>
         <v>9504</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B12" s="4" t="n">
         <f aca="false">(p_tech_hours_as_is-p_tech_hours_to_be)*p_anomalies_month*12*p_tech_rate</f>
         <v>1296</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B13" s="4" t="n">
         <f aca="false">B11+B12</f>
         <v>10800</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B14" s="6" t="n">
         <f aca="false">B13/12</f>
@@ -2265,22 +2331,22 @@
         <v>90</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B15" s="5" t="n">
         <f aca="false">p_price_hypothesis/B14</f>
         <v>0.144444444444444</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -2313,33 +2379,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="3" t="n">
@@ -2362,10 +2428,10 @@
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>4</v>
@@ -2390,10 +2456,10 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>5</v>
@@ -2418,10 +2484,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>3</v>
@@ -2446,10 +2512,10 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>4</v>
@@ -2488,53 +2554,57 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>171</v>
+        <v>178</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="D2" s="7" t="n">
         <v>4</v>
@@ -2546,22 +2616,26 @@
         <f aca="false">D2*E2</f>
         <v>20</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>175</v>
+      <c r="G2" s="7" t="str">
+        <f aca="false">IF(AND(D2&gt;=4,E2&gt;=4),"керувати тісно",IF(D2&gt;=4,"задовольняти",IF(E2&gt;=4,"інформувати","спостерігати")))</f>
+        <v>керувати тісно</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>176</v>
+        <v>183</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D3" s="7" t="n">
         <v>2</v>
@@ -2573,49 +2647,57 @@
         <f aca="false">D3*E3</f>
         <v>8</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>180</v>
+      <c r="G3" s="7" t="str">
+        <f aca="false">IF(AND(D3&gt;=4,E3&gt;=4),"керувати тісно",IF(D3&gt;=4,"задовольняти",IF(E3&gt;=4,"інформувати","спостерігати")))</f>
+        <v>інформувати</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>181</v>
+        <v>188</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>5</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" s="7" t="n">
         <f aca="false">D4*E4</f>
-        <v>15</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>185</v>
+        <v>20</v>
+      </c>
+      <c r="G4" s="7" t="str">
+        <f aca="false">IF(AND(D4&gt;=4,E4&gt;=4),"керувати тісно",IF(D4&gt;=4,"задовольняти",IF(E4&gt;=4,"інформувати","спостерігати")))</f>
+        <v>керувати тісно</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>186</v>
+        <v>193</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>4</v>
@@ -2627,22 +2709,26 @@
         <f aca="false">D5*E5</f>
         <v>16</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>190</v>
+      <c r="G5" s="7" t="str">
+        <f aca="false">IF(AND(D5&gt;=4,E5&gt;=4),"керувати тісно",IF(D5&gt;=4,"задовольняти",IF(E5&gt;=4,"інформувати","спостерігати")))</f>
+        <v>керувати тісно</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>191</v>
+        <v>198</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3</v>
@@ -2654,22 +2740,26 @@
         <f aca="false">D6*E6</f>
         <v>9</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>195</v>
+      <c r="G6" s="7" t="str">
+        <f aca="false">IF(AND(D6&gt;=4,E6&gt;=4),"керувати тісно",IF(D6&gt;=4,"задовольняти",IF(E6&gt;=4,"інформувати","спостерігати")))</f>
+        <v>спостерігати</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>3</v>
@@ -2681,22 +2771,26 @@
         <f aca="false">D7*E7</f>
         <v>6</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>200</v>
+      <c r="G7" s="7" t="str">
+        <f aca="false">IF(AND(D7&gt;=4,E7&gt;=4),"керувати тісно",IF(D7&gt;=4,"задовольняти",IF(E7&gt;=4,"інформувати","спостерігати")))</f>
+        <v>спостерігати</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>201</v>
+        <v>208</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>2</v>
@@ -2708,11 +2802,15 @@
         <f aca="false">D8*E8</f>
         <v>2</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>205</v>
+      <c r="G8" s="7" t="str">
+        <f aca="false">IF(AND(D8&gt;=4,E8&gt;=4),"керувати тісно",IF(D8&gt;=4,"задовольняти",IF(E8&gt;=4,"інформувати","спостерігати")))</f>
+        <v>спостерігати</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>206</v>
+        <v>213</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -2745,444 +2843,444 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>228</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>228</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>228</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>238</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>247</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="B21" s="7" t="n">
         <f aca="false">COUNTA(A2:A19)</f>
@@ -3191,7 +3289,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B22" s="7" t="n">
         <f aca="false">COUNTIF($A$2:$A$19,A22)</f>
@@ -3200,7 +3298,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B23" s="7" t="n">
         <f aca="false">COUNTIF($A$2:$A$19,A23)</f>
@@ -3209,7 +3307,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B24" s="7" t="n">
         <f aca="false">COUNTIF($A$2:$A$19,A24)</f>
@@ -3218,7 +3316,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="B25" s="7" t="n">
         <f aca="false">COUNTIF($A$2:$A$19,A25)</f>
@@ -3252,10 +3350,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>86</v>
@@ -3263,10 +3361,10 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="C2" s="8" t="n">
         <f aca="false">Цінність!B3/1000*p_cost_per_1000</f>
@@ -3278,7 +3376,7 @@
         <v>89</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="C3" s="8" t="n">
         <f aca="false">p_sim_month</f>
@@ -3287,10 +3385,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C4" s="8" t="n">
         <f aca="false">p_alerts_month*p_alert_price</f>
@@ -3299,10 +3397,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="C5" s="8" t="n">
         <f aca="false">p_support_hours*p_support_rate</f>
@@ -3311,10 +3409,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C6" s="8" t="n">
         <f aca="false">SUM(C2:C5)</f>
@@ -3323,10 +3421,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="C7" s="8" t="n">
         <f aca="false">p_fixed_platform</f>
@@ -3335,16 +3433,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3530,42 +3628,42 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>5</v>
@@ -3592,13 +3690,13 @@
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>5</v>
@@ -3625,13 +3723,13 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>4</v>
@@ -3658,13 +3756,13 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>4</v>
@@ -3691,13 +3789,13 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>4</v>
@@ -3724,13 +3822,13 @@
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>3</v>
@@ -3757,13 +3855,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>4</v>
@@ -3790,13 +3888,13 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>3</v>
@@ -3823,13 +3921,13 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>3</v>
@@ -3856,13 +3954,13 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>4</v>
@@ -3889,13 +3987,13 @@
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>2</v>
@@ -3922,13 +4020,13 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>3</v>

--- a/lab1/out/lab1_recalculated.xlsx
+++ b/lab1/out/lab1_recalculated.xlsx
@@ -73,7 +73,7 @@
     <t xml:space="preserve">Проблема і контекст</t>
   </si>
   <si>
-    <t xml:space="preserve">Енергоменеджер багатоорендного офісного центру дізнається про аномальне споживання лише з місячного рахунку, у середньому через 12 діб (П); причину перевитрат встановити складно, бо немає інтервальних даних по точках обліку. Втрати від аномалій оцінено в 3,4% річного споживання (П).</t>
+    <t xml:space="preserve">Енергоменеджер багатоорендного офісного центру виявляє аномальне споживання із запізненням (обходи, погодинні дані вводу або лише місячний рахунок): середнє і медіана 12 діб (П); причину перевитрат встановити складно, бо субоблік знімають вручну раз на місяць, а погодинні дані є лише по вводу, без інтервальних даних по точках обліку. Втрати від аномалій оцінено в 3,4% річного споживання (П).</t>
   </si>
   <si>
     <t xml:space="preserve">Первинний сегмент</t>
@@ -103,7 +103,7 @@
     <t xml:space="preserve">Ключова метрика</t>
   </si>
   <si>
-    <t xml:space="preserve">Медіана часу від початку аномалії до її фіксації: база 288 год (П), ціль: медіана не більше 2 год за 3 міс. пілоту; додатковий контроль хвоста розподілу: P80 не більше 4 год</t>
+    <t xml:space="preserve">Медіана часу від початку аномалії до її фіксації: база (медіана і середнє) 288 год (П), ціль: медіана не більше 2 год за 3 міс. пілоту; додатковий контроль хвоста розподілу: P80 не більше 4 год</t>
   </si>
   <si>
     <t xml:space="preserve">Межі MVP</t>
@@ -262,7 +262,7 @@
     <t xml:space="preserve">Тривалість аномалії до усунення, як є</t>
   </si>
   <si>
-    <t xml:space="preserve">частину виявляють обходом, решту після рахунку</t>
+    <t xml:space="preserve">середнє і медіана прийняті рівними 12 добам</t>
   </si>
   <si>
     <t xml:space="preserve">p_days_to_be</t>
@@ -745,7 +745,7 @@
     <t xml:space="preserve">так</t>
   </si>
   <si>
-    <t xml:space="preserve">Аналіз історичних 15-хв даних 3 будівель і розмітка аномалій</t>
+    <t xml:space="preserve">Аналіз історичних погодинних даних комерційного обліку по вводу 3 будівель і розмітка аномалій</t>
   </si>
   <si>
     <t xml:space="preserve">кількість будівель і місяців даних</t>
@@ -1481,7 +1481,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>

--- a/lab1/out/lab1_recalculated.xlsx
+++ b/lab1/out/lab1_recalculated.xlsx
@@ -73,7 +73,7 @@
     <t xml:space="preserve">Проблема і контекст</t>
   </si>
   <si>
-    <t xml:space="preserve">Енергоменеджер багатоорендного офісного центру виявляє аномальне споживання із запізненням (обходи, погодинні дані вводу або лише місячний рахунок): середнє і медіана 12 діб (П); причину перевитрат встановити складно, бо субоблік знімають вручну раз на місяць, а погодинні дані є лише по вводу, без інтервальних даних по точках обліку. Втрати від аномалій оцінено в 3,4% річного споживання (П).</t>
+    <t xml:space="preserve">Енергоменеджер багатоорендного офісного центру виявляє аномальне споживання із запізненням (обходи, погодинні дані вводу або лише місячний рахунок): у середньому 12 діб, медіана близько 11 діб, для бази округлена до 12 діб (П); причину перевитрат встановити складно, бо субоблік знімають вручну раз на місяць, а погодинні дані є лише по вводу, без інтервальних даних по точках обліку. Втрати від аномалій оцінено в 3,4% річного споживання (П).</t>
   </si>
   <si>
     <t xml:space="preserve">Первинний сегмент</t>
@@ -103,7 +103,7 @@
     <t xml:space="preserve">Ключова метрика</t>
   </si>
   <si>
-    <t xml:space="preserve">Медіана часу від початку аномалії до її фіксації: база (медіана і середнє) 288 год (П), ціль: медіана не більше 2 год за 3 міс. пілоту; додатковий контроль хвоста розподілу: P80 не більше 4 год</t>
+    <t xml:space="preserve">Медіана часу від початку аномалії до її фіксації: база 288 год (12 діб; медіана близько 11 діб, округлено, П), ціль: медіана не більше 2 год за 3 міс. пілоту; додатковий контроль хвоста розподілу: P80 не більше 4 год</t>
   </si>
   <si>
     <t xml:space="preserve">Межі MVP</t>
@@ -115,7 +115,7 @@
     <t xml:space="preserve">Головне припущення</t>
   </si>
   <si>
-    <t xml:space="preserve">A1: аномалії, які усуваються після рахунку, становлять не менше 2% річного споживання будівлі (вплив 5, невизначеність 4)</t>
+    <t xml:space="preserve">A1: втрати від аномалій, які зараз виявляють із запізненням (обходи, погодинні дані, рахунок), становлять не менше 2% річного споживання будівлі (вплив 5, невизначеність 4)</t>
   </si>
   <si>
     <t xml:space="preserve">Критерій переходу далі</t>
@@ -262,7 +262,7 @@
     <t xml:space="preserve">Тривалість аномалії до усунення, як є</t>
   </si>
   <si>
-    <t xml:space="preserve">середнє і медіана прийняті рівними 12 добам</t>
+    <t xml:space="preserve">середнє 12,2 доби, медіана близько 11 діб; обидва округлено до 12 діб</t>
   </si>
   <si>
     <t xml:space="preserve">p_days_to_be</t>
@@ -751,7 +751,7 @@
     <t xml:space="preserve">кількість будівель і місяців даних</t>
   </si>
   <si>
-    <t xml:space="preserve">Прототип шлюзу: мінікомп'ютер, адаптер RS-485, LTE модем</t>
+    <t xml:space="preserve">Тест A5: тимчасова збірка шлюзу (мінікомп'ютер, адаптер RS-485) в 1 будівлі на 2 тижні</t>
   </si>
   <si>
     <t xml:space="preserve">кількість тестових будівель</t>
@@ -823,16 +823,16 @@
     <t xml:space="preserve">кількість будівель, кількість ескалацій</t>
   </si>
   <si>
-    <t xml:space="preserve">Онбординг будівлі і підтримка</t>
+    <t xml:space="preserve">Підтримка будівлі: консультації клієнта, перевірка нестабільних лічильників (у v)</t>
   </si>
   <si>
     <t xml:space="preserve">кількість будівель і нестабільних лічильників</t>
   </si>
   <si>
-    <t xml:space="preserve">Супровід: виправлення, оновлення залежностей, нові моделі лічильників</t>
-  </si>
-  <si>
-    <t xml:space="preserve">кількість змін і моделей лічильників</t>
+    <t xml:space="preserve">Support і change команди: чергування, онбординг нових будівель, виправлення, оновлення, нові моделі лічильників</t>
+  </si>
+  <si>
+    <t xml:space="preserve">частки FTE команди супроводу; кількість змін</t>
   </si>
   <si>
     <t xml:space="preserve">Накладні: офіс, бухгалтерія, страхування відповідальності</t>
@@ -946,7 +946,7 @@
     <t xml:space="preserve">Цінність</t>
   </si>
   <si>
-    <t xml:space="preserve">Аномалії, які усуваються після рахунку, становлять не менше 2% річного споживання будівлі</t>
+    <t xml:space="preserve">Втрати від аномалій, які зараз виявляють із запізненням (обходи, погодинні дані, рахунок), становлять не менше 2% річного споживання будівлі</t>
   </si>
   <si>
     <t xml:space="preserve">A2</t>
@@ -1537,7 +1537,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
         <v>66</v>
       </c>
@@ -3140,7 +3140,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
         <v>248</v>
       </c>
@@ -3655,7 +3655,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>294</v>
       </c>

--- a/lab1/out/lab1_recalculated.xlsx
+++ b/lab1/out/lab1_recalculated.xlsx
@@ -394,7 +394,7 @@
     <t xml:space="preserve">будівель</t>
   </si>
   <si>
-    <t xml:space="preserve">умова варіанта ЛР № 4 і № 5</t>
+    <t xml:space="preserve">рядок варіанта 14 методичних вказівок до наступних робіт курсу</t>
   </si>
   <si>
     <t xml:space="preserve">p_mvp_months</t>
@@ -415,7 +415,7 @@
     <t xml:space="preserve">осіб</t>
   </si>
   <si>
-    <t xml:space="preserve">умова варіанта ЛР № 4 і № 5: BA/PM, 2 розробники, QA, DevOps</t>
+    <t xml:space="preserve">рядок варіанта 14 методичних вказівок до наступних робіт курсу: BA/PM, 2 розробники, QA, DevOps</t>
   </si>
   <si>
     <t xml:space="preserve">p_price_hypothesis</t>
@@ -2020,7 +2020,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
         <v>109</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
         <v>113</v>
       </c>
